--- a/avito_feed.xlsx
+++ b/avito_feed.xlsx
@@ -1459,7 +1459,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
@@ -6448,7 +6448,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KR20260622000</t>
+          <t>KR20260622040</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6474,17 +6474,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Конвейер ленточный (транспортер)</t>
+          <t>Ленточный конвейер горизонтальный</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «быстрый расчёт и сроки изготовления»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «быстрый расчёт и сроки изготовления»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/1tlsMfwLwpPa3g | https://yadi.sk/i/RWaDUWD0w7sXTA</t>
+          <t>https://yadi.sk/i/Ywo1YtB1PGV30w | https://yadi.sk/i/4qDRWU7gPCvpRA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>Пищевая промышленность</t>
+          <t>Химическая промышленность</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6579,7 +6579,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KR20260622001</t>
+          <t>KR20260622041</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ленточный транспортер. Конвейер ленточный</t>
+          <t>Ленточный конвейер для сыпучих материалов</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «экономия на персонале и окупаемость»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «экономия на персонале и окупаемость»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/iMrFNFUKG-czpg | https://yadi.sk/i/eAjqT3Y0SztyNg</t>
+          <t>https://yadi.sk/i/o1ZvtfZ0xxPLEw | https://yadi.sk/i/0fo1FW8OmY-vZw</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>70300</v>
+        <v>81200</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>Логистика и складирование</t>
+          <t>Лёгкая промышленность</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KR20260622002</t>
+          <t>KR20260622042</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6736,17 +6736,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Конвейер ленточный (транспортер) под заказ</t>
+          <t>Ленточный конвейер для штучных грузов</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «работа 24/7 и надёжность конструкции»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «работа 24/7 и надёжность конструкции»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/uKQDZRz18P5Fqw | https://yadi.sk/i/6_-vOPVnhNVUSA</t>
+          <t>https://yadi.sk/i/YUhgOA2s9zNY0A | https://yadi.sk/i/YD-0MQAbKF9TBA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>71000</v>
+        <v>81300</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>Сельское хозяйство</t>
+          <t>Пищевая промышленность</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KR20260622003</t>
+          <t>KR20260622043</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6867,15 +6867,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Леточный транспортер (конвейер)</t>
+          <t>Конвейер от производителя</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «любые размеры точно под ваш процесс»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «любые размеры точно под ваш процесс»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://yadi.sk/i/d6M4YimZHpcrZA | https://yadi.sk/i/EAnnFVZLhO6DYQ</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
@@ -6893,7 +6897,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>71200</v>
+        <v>81500</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -6944,7 +6948,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>Строительство и производство стройматериалов</t>
+          <t>Логистика и складирование</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6968,7 +6972,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KR20260622004</t>
+          <t>KR20260622044</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6994,17 +6998,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ленточный транспортер наклонный. Конвейер ленточный наклонный</t>
+          <t>Рольганг от производителя</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «пищевое исполнение и гигиеничность»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «пищевое исполнение и гигиеничность»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/Gys_GNmjD_k-cQ | https://yadi.sk/i/51qP-3Qoil6I4A</t>
+          <t>https://yadi.sk/i/tevnm_UlHiZrzA | https://yadi.sk/i/NQRjAF5ht_qpOw</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -7024,7 +7028,7 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>71300</v>
+        <v>81700</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -7063,7 +7067,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
@@ -7075,7 +7079,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>Химическая промышленность</t>
+          <t>Сельское хозяйство</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7099,7 +7103,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KR20260622005</t>
+          <t>KR20260622045</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7125,17 +7129,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Конвейер пластинчатый, транспортер цепной. Бесплатная доставка</t>
+          <t>Ленточный конвейер новый</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «мобильные версии и регулировка высоты»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «мобильные версии и регулировка высоты»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/A4KsilOKT9omqw | https://yadi.sk/d/cMdzXYqrzkVk-g</t>
+          <t>https://yadi.sk/i/voz3Q6mBTBZ10w | https://yadi.sk/i/2Uz0pwnmfDgA7w</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -7155,7 +7159,7 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>71500</v>
+        <v>81900</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -7206,7 +7210,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>Лёгкая промышленность</t>
+          <t>Строительство и производство стройматериалов</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7230,7 +7234,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KR20260622006</t>
+          <t>KR20260622046</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7256,17 +7260,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Конвейер ленточный (транспортер, элеватор)</t>
+          <t>Ленточный конвейер транспортер от производителя</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «интеграция в действующую линию»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «интеграция в действующую линию»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/3ypzO8E68LHFQA | https://yadi.sk/i/44bmsS738RFy-w</t>
+          <t>https://yadi.sk/d/LqpL31tdFiv3CA | https://yadi.sk/i/QixHigYoJZC5Dw</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -7286,7 +7290,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>72000</v>
+        <v>82100</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -7337,7 +7341,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>Пищевая промышленность</t>
+          <t>Химическая промышленность</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7361,7 +7365,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KR20260622007</t>
+          <t>KR20260622047</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7387,15 +7391,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ленточный конвейер от производителя</t>
+          <t>Ленточный конвейер (транспортер)прямой</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «бесплатная доставка и гарантия»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «бесплатная доставка и гарантия»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://yadi.sk/i/fLDF2STP5FbW_w | https://yadi.sk/i/J5f-fwiSdD2SIw</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
@@ -7413,7 +7421,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>72100</v>
+        <v>82700</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -7464,7 +7472,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>Логистика и складирование</t>
+          <t>Лёгкая промышленность</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7488,7 +7496,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KR20260622008</t>
+          <t>KR20260622048</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7514,17 +7522,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ленточный конвейер, транспортер</t>
+          <t>Ленточный транспортер с гарантией и доставкой</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «быстрый расчёт и сроки изготовления»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «быстрый расчёт и сроки изготовления»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/Dy0Tm23gRo9kgw | https://yadi.sk/i/w3zrHGgZR7YL7g</t>
+          <t>https://yadi.sk/i/CNM9Gy8AlkTl0Q | https://yadi.sk/d/2HjPJWbi0odBig</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -7544,7 +7552,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>72300</v>
+        <v>83000</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -7583,7 +7591,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
@@ -7595,7 +7603,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>Сельское хозяйство</t>
+          <t>Пищевая промышленность</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7619,7 +7627,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KR20260622009</t>
+          <t>KR20260622049</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7645,17 +7653,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ленточный конвейер, транспортер L и Z образные</t>
+          <t>Конвейер для сыпучих материалов</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «экономия на персонале и окупаемость»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «экономия на персонале и окупаемость»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/QBvlMzEe9FxiHg | https://yadi.sk/i/-hQgj2rzMJGnaw</t>
+          <t>https://yadi.sk/i/uDRWqsZrAYbApw | https://yadi.sk/i/KP9iFEdRvBeUtg</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -7675,7 +7683,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>72500</v>
+        <v>83100</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -7726,7 +7734,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>Строительство и производство стройматериалов</t>
+          <t>Логистика и складирование</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7750,7 +7758,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KR20260622010</t>
+          <t>KR20260622050</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7776,17 +7784,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ленточный конвейер с гарантией и доставкой</t>
+          <t>Конвейер ленточный (транспортер)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «работа 24/7 и надёжность конструкции»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «работа 24/7 и надёжность конструкции»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/xYrNKSaFp8-6Dw | https://yadi.sk/i/L3B5_yn6dOaQaA</t>
+          <t>https://yadi.sk/i/muGaFn_6UyFR6A | https://yadi.sk/i/r_gjOT0eJ_Q6Pg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -7806,7 +7814,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>72900</v>
+        <v>83200</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -7857,7 +7865,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>Химическая промышленность</t>
+          <t>Сельское хозяйство</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7881,7 +7889,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KR20260622011</t>
+          <t>KR20260622051</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7907,15 +7915,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ленточный конвейер, транспортер горизонтальный</t>
+          <t>Ленточный транспортер. Конвейер ленточный</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «любые размеры точно под ваш процесс»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «любые размеры точно под ваш процесс»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://yadi.sk/i/hrbITL1ZgRNgow | https://yadi.sk/i/n9gctTB9Gjv1qQ</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
@@ -7933,7 +7945,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>73000</v>
+        <v>83300</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -7984,7 +7996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>Лёгкая промышленность</t>
+          <t>Строительство и производство стройматериалов</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8008,7 +8020,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KR20260622012</t>
+          <t>KR20260622052</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8034,17 +8046,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ролики конвейерные</t>
+          <t>Конвейер ленточный (транспортер) под заказ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «пищевое исполнение и гигиеничность»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «пищевое исполнение и гигиеничность»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/bU4V-kDjtxEvzQ | https://yadi.sk/i/TjTAgceT7eHCGw</t>
+          <t>https://yadi.sk/i/ENTE3fr7u3srIw | https://yadi.sk/i/qlz2pECzuAaKWg</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -8064,7 +8076,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>73200</v>
+        <v>83400</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -8103,7 +8115,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W57" t="inlineStr"/>
@@ -8115,7 +8127,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>Пищевая промышленность</t>
+          <t>Химическая промышленность</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8139,7 +8151,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KR20260622013</t>
+          <t>KR20260622053</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8165,17 +8177,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ленточный транспортер от производителя</t>
+          <t>Леточный транспортер (конвейер)</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «мобильные версии и регулировка высоты»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «мобильные версии и регулировка высоты»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/mdBPy38ilxUepw | https://yadi.sk/d/2NU1nXe5fPG5Aw</t>
+          <t>https://yadi.sk/d/tgrlU3aMC0RCcA | https://yadi.sk/i/zy_Cy2FAUxcPIg</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -8195,7 +8207,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>73700</v>
+        <v>83500</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -8246,7 +8258,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Логистика и складирование</t>
+          <t>Лёгкая промышленность</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8270,7 +8282,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KR20260622014</t>
+          <t>KR20260622054</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8296,17 +8308,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Пластинчатый конвейер от производителя</t>
+          <t>Ленточный транспортер наклонный. Конвейер ленточный наклонный</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «интеграция в действующую линию»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «интеграция в действующую линию»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/_OzhfSfQpRVarQ | https://yadi.sk/i/7skbaRrnvIYioA</t>
+          <t>https://yadi.sk/i/pchT_unDDE2xDA | https://yadi.sk/i/Qh1eAf40lBrk8w</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -8326,7 +8338,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>74000</v>
+        <v>83700</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -8377,7 +8389,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>Сельское хозяйство</t>
+          <t>Пищевая промышленность</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8401,7 +8413,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KR20260622015</t>
+          <t>KR20260622055</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8427,15 +8439,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ленточный конвейер горизонтальный</t>
+          <t>Конвейер пластинчатый, транспортер цепной. Бесплатная доставка</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «бесплатная доставка и гарантия»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «бесплатная доставка и гарантия»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://yadi.sk/i/IAC8uGz3U3YdNw | https://yadi.sk/i/LqKQsUuKxH42kA</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
@@ -8453,7 +8469,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>74100</v>
+        <v>84500</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -8504,7 +8520,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>Строительство и производство стройматериалов</t>
+          <t>Логистика и складирование</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8528,7 +8544,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KR20260622016</t>
+          <t>KR20260622056</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8554,17 +8570,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ленточный конвейер для сыпучих материалов</t>
+          <t>Конвейер ленточный (транспортер, элеватор)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «быстрый расчёт и сроки изготовления»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «быстрый расчёт и сроки изготовления»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/6lmaNmONw1Fc6w | https://yadi.sk/i/3gpUjrruGrOUaA</t>
+          <t>https://yadi.sk/i/grVWMOX6htFnCg | https://yadi.sk/i/5EhP-p2d7eaaqQ</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -8584,7 +8600,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>75000</v>
+        <v>84800</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -8623,7 +8639,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W61" t="inlineStr"/>
@@ -8635,7 +8651,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>Химическая промышленность</t>
+          <t>Сельское хозяйство</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8659,7 +8675,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KR20260622017</t>
+          <t>KR20260622057</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8685,17 +8701,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ленточный конвейер для штучных грузов</t>
+          <t>Ленточный конвейер от производителя</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «экономия на персонале и окупаемость»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «экономия на персонале и окупаемость»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/Zlm0LYVVcKFW4A | https://yadi.sk/i/AdxvSaCho6DHpQ</t>
+          <t>https://yadi.sk/i/XnsZFRUAdCTisA | https://yadi.sk/i/veiQXAUpGEFdkg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -8715,7 +8731,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>75100</v>
+        <v>85200</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -8766,7 +8782,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>Лёгкая промышленность</t>
+          <t>Строительство и производство стройматериалов</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8790,7 +8806,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KR20260622018</t>
+          <t>KR20260622058</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8816,17 +8832,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Конвейер от производителя</t>
+          <t>Ленточный конвейер, транспортер</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «работа 24/7 и надёжность конструкции»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «работа 24/7 и надёжность конструкции»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/mp8DUszOfoySZw | https://yadi.sk/i/8uetLKLzHULnew</t>
+          <t>https://yadi.sk/i/yjeDWugLVOUbsw | https://yadi.sk/i/uFmGUjPbaPwd_A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -8846,7 +8862,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>75600</v>
+        <v>87400</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -8897,7 +8913,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>Пищевая промышленность</t>
+          <t>Химическая промышленность</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8921,7 +8937,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KR20260622019</t>
+          <t>KR20260622059</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8947,15 +8963,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Рольганг от производителя</t>
+          <t>Ленточный конвейер, транспортер L и Z образные</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «любые размеры точно под ваш процесс»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «любые размеры точно под ваш процесс»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://yadi.sk/i/78pWtYbaicMAPw | https://yadi.sk/i/S0v3YSsxHreY7g</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
@@ -8973,7 +8993,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>75700</v>
+        <v>87600</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -9024,7 +9044,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>Логистика и складирование</t>
+          <t>Лёгкая промышленность</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9048,7 +9068,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KR20260622020</t>
+          <t>KR20260622060</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9074,17 +9094,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ленточный конвейер новый</t>
+          <t>Ленточный конвейер с гарантией и доставкой</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «пищевое исполнение и гигиеничность»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «пищевое исполнение и гигиеничность»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/0wWvlRdbe7yLPg | https://yadi.sk/i/HPLKdNJM8M_SaQ</t>
+          <t>https://yadi.sk/i/9oI_270MmZ6X7g | https://yadi.sk/i/pIz7bLYfK6Q9VQ</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -9104,7 +9124,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>76200</v>
+        <v>87800</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -9143,7 +9163,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W65" t="inlineStr"/>
@@ -9155,7 +9175,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>Сельское хозяйство</t>
+          <t>Пищевая промышленность</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9179,7 +9199,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KR20260622021</t>
+          <t>KR20260622061</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9205,17 +9225,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ленточный конвейер транспортер от производителя</t>
+          <t>Ленточный конвейер, транспортер горизонтальный</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «мобильные версии и регулировка высоты»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «мобильные версии и регулировка высоты»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/gSh0-bVGdVZTMQ | https://yadi.sk/i/uThUplNckitb7Q</t>
+          <t>https://yadi.sk/i/kOUHe1RllQrwlA | https://yadi.sk/i/BVQcCpHG2GTM8A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -9235,7 +9255,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>76300</v>
+        <v>88100</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -9286,7 +9306,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>Строительство и производство стройматериалов</t>
+          <t>Логистика и складирование</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9310,7 +9330,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KR20260622022</t>
+          <t>KR20260622062</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9336,17 +9356,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ленточный конвейер (транспортер)прямой</t>
+          <t>Ролики конвейерные</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «интеграция в действующую линию»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «интеграция в действующую линию»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/sampTaU7-ZHIHg | https://yadi.sk/i/A8nHVOL6VZcXXw</t>
+          <t>https://yadi.sk/i/ynt_cx30-M4brA | https://yadi.sk/i/asIzaxlqH4B3ow</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -9366,7 +9386,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>76700</v>
+        <v>88300</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -9417,7 +9437,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>Химическая промышленность</t>
+          <t>Сельское хозяйство</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9441,7 +9461,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KR20260622023</t>
+          <t>KR20260622063</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9467,15 +9487,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ленточный транспортер с гарантией и доставкой</t>
+          <t>Ленточный транспортер от производителя</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «бесплатная доставка и гарантия»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «бесплатная доставка и гарантия»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://yadi.sk/i/fjIlTxyTu54A5w | https://yadi.sk/i/VD3LxVcHGyQPQw</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
@@ -9493,7 +9517,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>76900</v>
+        <v>88400</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -9544,7 +9568,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>Лёгкая промышленность</t>
+          <t>Строительство и производство стройматериалов</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9568,7 +9592,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KR20260622024</t>
+          <t>KR20260622064</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9594,17 +9618,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Конвейер для сыпучих материалов</t>
+          <t>Пластинчатый конвейер от производителя</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «быстрый расчёт и сроки изготовления»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «быстрый расчёт и сроки изготовления»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/4bAfQL-4M1osNQ | https://yadi.sk/i/ssZ7s2E2VFOTNg</t>
+          <t>https://yadi.sk/i/dDGaRlYX7-3-dA | https://yadi.sk/i/RdPTTn9BeAm_Kg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -9624,7 +9648,7 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>77200</v>
+        <v>89000</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -9663,7 +9687,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W69" t="inlineStr"/>
@@ -9675,7 +9699,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>Пищевая промышленность</t>
+          <t>Химическая промышленность</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9699,7 +9723,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KR20260622025</t>
+          <t>KR20260622065</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9725,17 +9749,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Конвейер ленточный (транспортер)</t>
+          <t>Ленточный конвейер горизонтальный</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «экономия на персонале и окупаемость»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «экономия на персонале и окупаемость»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/V9D79bGIjI_Yyw | https://yadi.sk/i/1m4xp8HdCZLVOw</t>
+          <t>https://yadi.sk/i/D1EvZSRTYnFJVQ | https://yadi.sk/i/kDsPiGjlwrFIsQ</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -9755,7 +9779,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>77300</v>
+        <v>91000</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -9806,7 +9830,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>Логистика и складирование</t>
+          <t>Лёгкая промышленность</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9830,7 +9854,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KR20260622026</t>
+          <t>KR20260622066</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9856,17 +9880,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ленточный транспортер. Конвейер ленточный</t>
+          <t>Ленточный конвейер для сыпучих материалов</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «работа 24/7 и надёжность конструкции»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «работа 24/7 и надёжность конструкции»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/bZt8Bm3DH5ub6A | https://yadi.sk/i/-D_RwnaW-PbEMw</t>
+          <t>https://yadi.sk/i/7nlIWGYK7U9CYw | https://downloader.disk.yandex.ru/disk/89af0cfe0fa142178efd7a200b4c28dbbd0e68e80a2dd48970b2d85e38aeaf18/6a397378/cGlVQwgwRygpL7ZX0O1AqvoNHj-HioKsylc66EB1RalZg5JpxiZSkZisTE3Dwg0x94G8m8aip_l9ZDRbpyUIbA%3D%3D?uid=2364731203&amp;filename=KR20260622066_2.jpg&amp;disposition=attachment&amp;hash=&amp;limit=0&amp;content_type=image%2Fjpeg&amp;owner_uid=2364731203&amp;fsize=308918&amp;hid=813bbe2de2711cd5572d337aca9160d0&amp;media_type=image&amp;tknv=v3&amp;is_direct_zip_experiment=1&amp;etag=eda22e6aaa3b212d7dd40562dbcac00d</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -9886,7 +9910,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>77600</v>
+        <v>91200</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -9937,7 +9961,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>Сельское хозяйство</t>
+          <t>Пищевая промышленность</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9961,7 +9985,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KR20260622027</t>
+          <t>KR20260622067</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9987,15 +10011,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Конвейер ленточный (транспортер) под заказ</t>
+          <t>Ленточный конвейер для штучных грузов</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «любые размеры точно под ваш процесс»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «любые размеры точно под ваш процесс»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://yadi.sk/i/C1C_YwTs8neTrQ | https://yadi.sk/i/rZzAIDKBjRElEg</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
@@ -10013,7 +10041,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>77800</v>
+        <v>92100</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -10064,7 +10092,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>Строительство и производство стройматериалов</t>
+          <t>Логистика и складирование</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10088,7 +10116,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KR20260622028</t>
+          <t>KR20260622068</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10114,17 +10142,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Леточный транспортер (конвейер)</t>
+          <t>Конвейер от производителя</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «пищевое исполнение и гигиеничность»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «пищевое исполнение и гигиеничность»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/-awNwNh-UNUP6A | https://yadi.sk/i/eHsas9QLfNs5Tw</t>
+          <t>https://yadi.sk/i/9L3G8ZTnzgImDA | https://yadi.sk/i/LYBVp3iNrOY8fg</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
@@ -10144,7 +10172,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>78000</v>
+        <v>92400</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -10183,7 +10211,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W73" t="inlineStr"/>
@@ -10195,7 +10223,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>Химическая промышленность</t>
+          <t>Сельское хозяйство</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10219,7 +10247,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KR20260622029</t>
+          <t>KR20260622069</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10245,17 +10273,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ленточный транспортер наклонный. Конвейер ленточный наклонный</t>
+          <t>Рольганг от производителя</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «мобильные версии и регулировка высоты»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «мобильные версии и регулировка высоты»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/aKUdX48ZsRc2Ow | https://yadi.sk/i/ZUpd_b1uHm04-A</t>
+          <t>https://yadi.sk/i/5kA9fMJqiOA9hQ | https://yadi.sk/i/R-OpeLP5EOfWcA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
@@ -10275,7 +10303,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>78100</v>
+        <v>93400</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -10326,7 +10354,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>Лёгкая промышленность</t>
+          <t>Строительство и производство стройматериалов</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10350,7 +10378,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KR20260622030</t>
+          <t>KR20260622070</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10376,17 +10404,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Конвейер пластинчатый, транспортер цепной. Бесплатная доставка</t>
+          <t>Ленточный конвейер новый</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «интеграция в действующую линию»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «интеграция в действующую линию»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/CzUf4rNxeUpE9w | https://yadi.sk/i/TegU4USpnc2jEQ</t>
+          <t>https://yadi.sk/i/MXDFyBgV_QF2ZQ | https://yadi.sk/i/mzLBAFZAUx3RbA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
@@ -10406,7 +10434,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>78300</v>
+        <v>94000</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -10457,7 +10485,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>Пищевая промышленность</t>
+          <t>Химическая промышленность</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10481,7 +10509,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KR20260622031</t>
+          <t>KR20260622071</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10507,15 +10535,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Конвейер ленточный (транспортер, элеватор)</t>
+          <t>Ленточный конвейер транспортер от производителя</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «бесплатная доставка и гарантия»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «бесплатная доставка и гарантия»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://yadi.sk/i/Ua8VUtTqI2L7lQ | https://yadi.sk/i/fsMg01m1u2qKuQ</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
@@ -10533,7 +10565,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>78400</v>
+        <v>97600</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -10584,7 +10616,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>Логистика и складирование</t>
+          <t>Лёгкая промышленность</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10608,7 +10640,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KR20260622032</t>
+          <t>KR20260622072</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10634,17 +10666,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ленточный конвейер от производителя</t>
+          <t>Ленточный конвейер (транспортер)прямой</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «быстрый расчёт и сроки изготовления»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «быстрый расчёт и сроки изготовления»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/YxFxRb1lC6rFOQ | https://yadi.sk/i/ZYpyo9m-9pELQA</t>
+          <t>https://yadi.sk/i/HNOKkfNr5lc8rA | https://yadi.sk/i/TGq5pBkUJ76PMg</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
@@ -10664,7 +10696,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>78500</v>
+        <v>70000</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -10703,7 +10735,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W77" t="inlineStr"/>
@@ -10715,7 +10747,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>Сельское хозяйство</t>
+          <t>Пищевая промышленность</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10739,7 +10771,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KR20260622033</t>
+          <t>KR20260622073</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10765,17 +10797,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ленточный конвейер, транспортер</t>
+          <t>Ленточный транспортер с гарантией и доставкой</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «экономия на персонале и окупаемость»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «экономия на персонале и окупаемость»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://yadi.sk/d/TMJSgbVU4G8eSQ | https://yadi.sk/i/ztzJMCE9gCgk4Q</t>
+          <t>https://yadi.sk/i/N5Y9z-UnHsKirw | https://yadi.sk/i/NBDO9D1qW5UnOA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
@@ -10795,7 +10827,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>78900</v>
+        <v>70300</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -10846,7 +10878,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>Строительство и производство стройматериалов</t>
+          <t>Логистика и складирование</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10870,7 +10902,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KR20260622034</t>
+          <t>KR20260622074</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10896,17 +10928,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ленточный конвейер, транспортер L и Z образные</t>
+          <t>Конвейер для сыпучих материалов</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «работа 24/7 и надёжность конструкции»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «работа 24/7 и надёжность конструкции»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/X1NbqksAKmeISQ | https://yadi.sk/i/bxyfIO5GyRh_lg</t>
+          <t>https://yadi.sk/i/IdyG7GgWm1umCQ | https://yadi.sk/i/6LoKW2qb1gVbsA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
@@ -10926,7 +10958,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>79100</v>
+        <v>71000</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -10977,7 +11009,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>Химическая промышленность</t>
+          <t>Сельское хозяйство</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11001,7 +11033,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KR20260622035</t>
+          <t>KR20260622075</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -11027,15 +11059,19 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ленточный конвейер с гарантией и доставкой</t>
+          <t>Конвейер ленточный (транспортер)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «любые размеры точно под ваш процесс»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «любые размеры точно под ваш процесс»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://yadi.sk/i/R_BGrZJUSs_Rww | https://yadi.sk/i/0vMQ8TawZ3EuEQ</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
@@ -11053,7 +11089,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>79200</v>
+        <v>71200</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -11104,7 +11140,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>Лёгкая промышленность</t>
+          <t>Строительство и производство стройматериалов</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11128,7 +11164,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>KR20260622036</t>
+          <t>KR20260622076</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -11154,17 +11190,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ленточный конвейер, транспортер горизонтальный</t>
+          <t>Ленточный транспортер. Конвейер ленточный</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «пищевое исполнение и гигиеничность»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «пищевое исполнение и гигиеничность»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: переработка и сортировка (сыпучие материалы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/_hXyQrmIU2eUQQ | https://yadi.sk/i/cJiiZg5E42J_cA</t>
+          <t>https://yadi.sk/i/eXORZweZZ1M7aQ | https://yadi.sk/i/57ixTecfDfYijQ</t>
         </is>
       </c>
       <c r="J81" t="inlineStr"/>
@@ -11184,7 +11220,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>79300</v>
+        <v>71300</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -11223,7 +11259,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Горизонтальный</t>
+          <t>Наклонный</t>
         </is>
       </c>
       <c r="W81" t="inlineStr"/>
@@ -11235,7 +11271,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>Пищевая промышленность</t>
+          <t>Химическая промышленность</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11259,7 +11295,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KR20260622037</t>
+          <t>KR20260622077</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -11285,17 +11321,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ролики конвейерные</t>
+          <t>Конвейер ленточный (транспортер) под заказ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «мобильные версии и регулировка высоты»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «мобильные версии и регулировка высоты»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: производственные линии (штучные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/vf0BZilM2DHNhw | https://yadi.sk/i/fXQPCcSvaKRjJg</t>
+          <t>https://yadi.sk/d/_hBIOKBxcN1B8g | https://yadi.sk/i/OsElRx9VFnPkCQ</t>
         </is>
       </c>
       <c r="J82" t="inlineStr"/>
@@ -11315,7 +11351,7 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>79400</v>
+        <v>71500</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -11366,7 +11402,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>Логистика и складирование</t>
+          <t>Лёгкая промышленность</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11390,7 +11426,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KR20260622038</t>
+          <t>KR20260622078</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -11416,17 +11452,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ленточный транспортер от производителя</t>
+          <t>Леточный транспортер (конвейер)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «интеграция в действующую линию»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: сельское хозяйство (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «интеграция в действующую линию»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: пищевая промышленность (упакованная продукция)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://yadi.sk/i/ARCsG7wakdMqyw | https://yadi.sk/i/960Yn8KgI4ixhg</t>
+          <t>https://yadi.sk/i/GY1PItk7Ouc5IA | https://yadi.sk/i/AqoEtKFJR6goYw</t>
         </is>
       </c>
       <c r="J83" t="inlineStr"/>
@@ -11446,7 +11482,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>79800</v>
+        <v>72000</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -11497,7 +11533,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>Сельское хозяйство</t>
+          <t>Пищевая промышленность</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11521,7 +11557,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KR20260622039</t>
+          <t>KR20260622079</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -11547,15 +11583,19 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Пластинчатый конвейер от производителя</t>
+          <t>Ленточный транспортер наклонный. Конвейер ленточный наклонный</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «бесплатная доставка и гарантия»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: строительные материалы (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>🏭 &lt;strong&gt;Производство ленточных конвейеров по индивидуальным размерам&lt;/strong&gt;&lt;br/&gt;&lt;br/&gt;✅ Изготовим под вашу задачу — акцент на «бесплатная доставка и гарантия»&lt;br/&gt;☎ Точную цену рассчитаем во время звонка&lt;br/&gt;🚛 Доставка по всей России&lt;br/&gt;&lt;br/&gt;📏 Характеристики (под заказ):&lt;br/&gt;▸ Длина: 0,5–10 м&lt;br/&gt;▸ Ширина ленты: 100–700 мм&lt;br/&gt;▸ Скорость: от 0,5 м/с&lt;br/&gt;▸ Мощность: от 0,25 кВт&lt;br/&gt;&lt;br/&gt;🛠 Конфигурации: прямой, наклонный, Г / L / Z-образный&lt;br/&gt;🔩 Материал: сталь или нержавейка AISI 304&lt;br/&gt;&lt;br/&gt;⚙ Подходит для: логистика и склады (навалочные грузы)&lt;br/&gt;✔ Регулятор скорости ✔ Борта ✔ Лопатки ✔ Гофроборт ✔ Колёсные опоры&lt;br/&gt;&lt;br/&gt;☎ Звоните — поможем подобрать и посчитаем стоимость!  [ДЕМО-ТЕКСТ: подключите ANTHROPIC_API_KEY для уникальных описаний]</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://yadi.sk/i/2FSsG2uP1V8QjA | https://yadi.sk/i/REYKzxiixWk-xQ</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
@@ -11573,7 +11613,7 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>79900</v>
+        <v>72100</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -11624,7 +11664,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>Строительство и производство стройматериалов</t>
+          <t>Логистика и складирование</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
